--- a/审核导出/silicone_watercolor_ink_审核.xlsx
+++ b/审核导出/silicone_watercolor_ink_审核.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>作水彩涂畫的趣味應用功能。</t>
+          <t>作水彩塗畫的趣味應用功能。</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -744,12 +744,12 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
